--- a/Tools/Luban/DataTables/Datas/__beans__.xlsx
+++ b/Tools/Luban/DataTables/Datas/__beans__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangwencheng/UnityProject/2025TTGJ/Tools/Luban/DataTables/Datas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFEF523B-2DDE-054D-840B-1A7349A84DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4602FD75-62E5-4FE8-BB4E-6C63791FB72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31540" yWindow="1860" windowWidth="14880" windowHeight="16180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -156,114 +156,6 @@
   </si>
   <si>
     <t>y3</t>
-  </si>
-  <si>
-    <t>test.Shape</t>
-  </si>
-  <si>
-    <t>test.Circle</t>
-  </si>
-  <si>
-    <t>Shape</t>
-  </si>
-  <si>
-    <t>圆</t>
-  </si>
-  <si>
-    <t>radius</t>
-  </si>
-  <si>
-    <t>半径</t>
-  </si>
-  <si>
-    <t>test2.Rectangle</t>
-  </si>
-  <si>
-    <t>矩形</t>
-  </si>
-  <si>
-    <t>width</t>
-  </si>
-  <si>
-    <t>宽度</t>
-  </si>
-  <si>
-    <t>height</t>
-  </si>
-  <si>
-    <t>高度</t>
-  </si>
-  <si>
-    <t>#</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>item.useParam</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>use</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>itemid</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>price</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用类型</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>道具id</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>售价</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>item表使用效果</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>宝可梦进化</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>进化等级</t>
-  </si>
-  <si>
-    <t>pokemonID</t>
-  </si>
-  <si>
-    <t>目标ID</t>
-  </si>
-  <si>
-    <t>PokemonEvolution</t>
-  </si>
-  <si>
-    <t>PokemonAISkill</t>
-  </si>
-  <si>
-    <t>AI宝可梦Skill选择</t>
-  </si>
-  <si>
-    <t>skillID</t>
-  </si>
-  <si>
-    <t>技能Id</t>
-  </si>
-  <si>
-    <t>probability</t>
-  </si>
-  <si>
-    <t>释放概率</t>
   </si>
 </sst>
 </file>
@@ -274,14 +166,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -289,7 +181,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -297,14 +189,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -312,7 +204,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -375,9 +267,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Bad" xfId="2" builtinId="27"/>
-    <cellStyle name="Good" xfId="1" builtinId="26"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="差" xfId="2" builtinId="27"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -651,7 +543,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.5" customWidth="1"/>
     <col min="3" max="8" width="19.6640625" customWidth="1"/>
@@ -659,7 +551,7 @@
     <col min="10" max="13" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -697,7 +589,7 @@
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -723,7 +615,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -758,7 +650,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -781,7 +673,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -795,7 +687,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -809,7 +701,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -823,7 +715,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -843,7 +735,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -857,7 +749,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -871,193 +763,51 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" t="s">
-        <v>44</v>
-      </c>
-      <c r="J13" t="s">
-        <v>45</v>
-      </c>
-      <c r="L13" t="s">
-        <v>35</v>
-      </c>
-      <c r="N13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" t="s">
-        <v>48</v>
-      </c>
-      <c r="J14" t="s">
-        <v>49</v>
-      </c>
-      <c r="L14" t="s">
-        <v>35</v>
-      </c>
-      <c r="N14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>13</v>
-      </c>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="F15" s="2"/>
-      <c r="J15" t="s">
-        <v>51</v>
-      </c>
-      <c r="L15" t="s">
-        <v>35</v>
-      </c>
-      <c r="N15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="L17" t="s">
-        <v>27</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="L18" t="s">
-        <v>27</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="N16" s="2"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="J17" s="2"/>
+      <c r="N17" s="2"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="J18" s="2"/>
+      <c r="N18" s="2"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
       <c r="J19" s="2"/>
       <c r="N19" s="2"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="J21" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B23" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="J24" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>73</v>
-      </c>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="J21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="J24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="N24" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Tools/Luban/DataTables/Datas/__beans__.xlsx
+++ b/Tools/Luban/DataTables/Datas/__beans__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1_Game_Data\Unity\2025TTGJ\Tools\Luban\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangwencheng/UnityProject/2025TTGJ/Tools/Luban/DataTables/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4602FD75-62E5-4FE8-BB4E-6C63791FB72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6492636-95B1-8F49-B840-1AFB83BE8441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="80">
   <si>
     <t>##var</t>
   </si>
@@ -156,6 +156,132 @@
   </si>
   <si>
     <t>y3</t>
+  </si>
+  <si>
+    <t>test.Shape</t>
+  </si>
+  <si>
+    <t>test.Circle</t>
+  </si>
+  <si>
+    <t>Shape</t>
+  </si>
+  <si>
+    <t>圆</t>
+  </si>
+  <si>
+    <t>radius</t>
+  </si>
+  <si>
+    <t>半径</t>
+  </si>
+  <si>
+    <t>test2.Rectangle</t>
+  </si>
+  <si>
+    <t>矩形</t>
+  </si>
+  <si>
+    <t>width</t>
+  </si>
+  <si>
+    <t>宽度</t>
+  </si>
+  <si>
+    <t>height</t>
+  </si>
+  <si>
+    <t>高度</t>
+  </si>
+  <si>
+    <t>#</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>item.useParam</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>use</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>itemid</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>price</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用类型</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>道具id</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>售价</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>item表使用效果</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>宝可梦进化</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>进化等级</t>
+  </si>
+  <si>
+    <t>pokemonID</t>
+  </si>
+  <si>
+    <t>目标ID</t>
+  </si>
+  <si>
+    <t>PokemonEvolution</t>
+  </si>
+  <si>
+    <t>PokemonAISkill</t>
+  </si>
+  <si>
+    <t>AI宝可梦Skill选择</t>
+  </si>
+  <si>
+    <t>skillID</t>
+  </si>
+  <si>
+    <t>技能Id</t>
+  </si>
+  <si>
+    <t>probability</t>
+  </si>
+  <si>
+    <t>释放概率</t>
+  </si>
+  <si>
+    <t>ItemConfig</t>
+  </si>
+  <si>
+    <t>道具配置</t>
+  </si>
+  <si>
+    <t>ItemId</t>
+  </si>
+  <si>
+    <t>道具ID</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>道具数量</t>
   </si>
 </sst>
 </file>
@@ -166,14 +292,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -181,7 +307,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -189,14 +315,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -204,7 +330,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -267,9 +393,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="差" xfId="2" builtinId="27"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -542,8 +668,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:P26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.5" customWidth="1"/>
     <col min="3" max="8" width="19.6640625" customWidth="1"/>
@@ -551,7 +677,7 @@
     <col min="10" max="13" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -589,7 +715,7 @@
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -615,7 +741,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -650,7 +776,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -673,7 +799,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -687,7 +813,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -701,7 +827,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -715,7 +841,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -735,7 +861,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -749,7 +875,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -763,51 +889,241 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" t="s">
+        <v>45</v>
+      </c>
+      <c r="L13" t="s">
+        <v>35</v>
+      </c>
+      <c r="N13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" t="s">
+        <v>35</v>
+      </c>
+      <c r="N14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
       <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="N16" s="2"/>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="J17" s="2"/>
-      <c r="N17" s="2"/>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="J18" s="2"/>
-      <c r="N18" s="2"/>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="J15" t="s">
+        <v>51</v>
+      </c>
+      <c r="L15" t="s">
+        <v>35</v>
+      </c>
+      <c r="N15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L17" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L18" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="J19" s="2"/>
       <c r="N19" s="2"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="J21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="J24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="N24" s="3"/>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B25" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="J26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>79</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Tools/Luban/DataTables/Datas/__beans__.xlsx
+++ b/Tools/Luban/DataTables/Datas/__beans__.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangwencheng/UnityProject/2025TTGJ/Tools/Luban/DataTables/Datas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6492636-95B1-8F49-B840-1AFB83BE8441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E890E300-566F-0144-92D1-5B4DE9EE9B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="74">
   <si>
     <t>##var</t>
   </si>
@@ -264,24 +264,6 @@
   </si>
   <si>
     <t>释放概率</t>
-  </si>
-  <si>
-    <t>ItemConfig</t>
-  </si>
-  <si>
-    <t>道具配置</t>
-  </si>
-  <si>
-    <t>ItemId</t>
-  </si>
-  <si>
-    <t>道具ID</t>
-  </si>
-  <si>
-    <t>count</t>
-  </si>
-  <si>
-    <t>道具数量</t>
   </si>
 </sst>
 </file>
@@ -668,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.5" customWidth="1"/>
@@ -1097,34 +1079,6 @@
         <v>73</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B25" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N25" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="J26" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>
